--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1951DA8-BDE0-4DAE-BBB1-3F2098FE408A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AE475D-EAF2-4E54-BCA5-6E89233FD4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61530" yWindow="915" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="66240" yWindow="915" windowWidth="18630" windowHeight="9465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Concurso</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>Bola6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -109,13 +112,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G503"/>
+  <dimension ref="A1:G506"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -11992,26 +11993,77 @@
       </c>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A503" s="2">
+      <c r="A503">
         <v>3046</v>
       </c>
-      <c r="B503" s="3">
+      <c r="B503">
         <v>16</v>
       </c>
-      <c r="C503" s="3">
+      <c r="C503">
         <v>23</v>
       </c>
-      <c r="D503" s="3">
+      <c r="D503">
         <v>24</v>
       </c>
-      <c r="E503" s="3">
+      <c r="E503">
         <v>33</v>
       </c>
-      <c r="F503" s="3">
+      <c r="F503">
         <v>36</v>
       </c>
-      <c r="G503" s="3">
+      <c r="G503">
         <v>52</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A504">
+        <v>3047</v>
+      </c>
+      <c r="B504">
+        <v>4</v>
+      </c>
+      <c r="C504">
+        <v>18</v>
+      </c>
+      <c r="D504">
+        <v>22</v>
+      </c>
+      <c r="E504">
+        <v>26</v>
+      </c>
+      <c r="F504">
+        <v>31</v>
+      </c>
+      <c r="G504">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="505" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A505">
+        <v>3047</v>
+      </c>
+      <c r="B505">
+        <v>2</v>
+      </c>
+      <c r="C505">
+        <v>6</v>
+      </c>
+      <c r="D505">
+        <v>27</v>
+      </c>
+      <c r="E505">
+        <v>39</v>
+      </c>
+      <c r="F505">
+        <v>44</v>
+      </c>
+      <c r="G505">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B506" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -12021,15 +12073,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12197,6 +12240,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12208,14 +12260,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12235,6 +12279,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AE475D-EAF2-4E54-BCA5-6E89233FD4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0496955-7041-4BBF-AA08-1FD9B8C1FDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="66240" yWindow="915" windowWidth="18630" windowHeight="9465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="60300" yWindow="6345" windowWidth="24705" windowHeight="9000" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Concurso</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>Bola6</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -437,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G506"/>
+  <dimension ref="A1:G507"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -12062,8 +12059,49 @@
       </c>
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="B506" t="s">
-        <v>7</v>
+      <c r="A506">
+        <v>3048</v>
+      </c>
+      <c r="B506">
+        <v>2</v>
+      </c>
+      <c r="C506">
+        <v>6</v>
+      </c>
+      <c r="D506">
+        <v>27</v>
+      </c>
+      <c r="E506">
+        <v>39</v>
+      </c>
+      <c r="F506">
+        <v>44</v>
+      </c>
+      <c r="G506">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A507">
+        <v>3049</v>
+      </c>
+      <c r="B507">
+        <v>6</v>
+      </c>
+      <c r="C507">
+        <v>13</v>
+      </c>
+      <c r="D507">
+        <v>36</v>
+      </c>
+      <c r="E507">
+        <v>43</v>
+      </c>
+      <c r="F507">
+        <v>53</v>
+      </c>
+      <c r="G507">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -12073,6 +12111,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12240,15 +12287,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12260,6 +12298,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12279,14 +12325,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0496955-7041-4BBF-AA08-1FD9B8C1FDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E294B716-35DD-478F-99F8-1EAD1A8874B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60300" yWindow="6345" windowWidth="24705" windowHeight="9000" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="71835" yWindow="465" windowWidth="14565" windowHeight="13800" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G507"/>
+  <dimension ref="A1:G508"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -12104,6 +12104,29 @@
         <v>55</v>
       </c>
     </row>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A508">
+        <v>3050</v>
+      </c>
+      <c r="B508">
+        <v>11</v>
+      </c>
+      <c r="C508">
+        <v>14</v>
+      </c>
+      <c r="D508">
+        <v>30</v>
+      </c>
+      <c r="E508">
+        <v>38</v>
+      </c>
+      <c r="F508">
+        <v>49</v>
+      </c>
+      <c r="G508">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -12111,15 +12134,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12287,6 +12301,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12298,14 +12321,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12325,6 +12340,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E294B716-35DD-478F-99F8-1EAD1A8874B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25E5D1B-971A-414E-8466-796F2482074D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71835" yWindow="465" windowWidth="14565" windowHeight="13800" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="2310" yWindow="1553" windowWidth="23505" windowHeight="10350" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -109,11 +109,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G508"/>
+  <dimension ref="A1:G513"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -12127,6 +12129,121 @@
         <v>55</v>
       </c>
     </row>
+    <row r="509" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A509" s="2">
+        <v>3051</v>
+      </c>
+      <c r="B509" s="3">
+        <v>11</v>
+      </c>
+      <c r="C509" s="3">
+        <v>15</v>
+      </c>
+      <c r="D509" s="3">
+        <v>20</v>
+      </c>
+      <c r="E509" s="3">
+        <v>21</v>
+      </c>
+      <c r="F509" s="3">
+        <v>38</v>
+      </c>
+      <c r="G509" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A510" s="2">
+        <v>3052</v>
+      </c>
+      <c r="B510" s="3">
+        <v>16</v>
+      </c>
+      <c r="C510" s="3">
+        <v>30</v>
+      </c>
+      <c r="D510" s="3">
+        <v>40</v>
+      </c>
+      <c r="E510" s="3">
+        <v>47</v>
+      </c>
+      <c r="F510" s="3">
+        <v>48</v>
+      </c>
+      <c r="G510" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A511" s="2">
+        <v>3053</v>
+      </c>
+      <c r="B511" s="3">
+        <v>1</v>
+      </c>
+      <c r="C511" s="3">
+        <v>13</v>
+      </c>
+      <c r="D511" s="3">
+        <v>25</v>
+      </c>
+      <c r="E511" s="3">
+        <v>35</v>
+      </c>
+      <c r="F511" s="3">
+        <v>39</v>
+      </c>
+      <c r="G511" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="512" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A512" s="2">
+        <v>3054</v>
+      </c>
+      <c r="B512" s="3">
+        <v>8</v>
+      </c>
+      <c r="C512" s="3">
+        <v>17</v>
+      </c>
+      <c r="D512" s="3">
+        <v>24</v>
+      </c>
+      <c r="E512" s="3">
+        <v>43</v>
+      </c>
+      <c r="F512" s="3">
+        <v>47</v>
+      </c>
+      <c r="G512" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="513" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A513" s="2">
+        <v>3055</v>
+      </c>
+      <c r="B513" s="3">
+        <v>1</v>
+      </c>
+      <c r="C513" s="3">
+        <v>11</v>
+      </c>
+      <c r="D513" s="3">
+        <v>36</v>
+      </c>
+      <c r="E513" s="3">
+        <v>43</v>
+      </c>
+      <c r="F513" s="3">
+        <v>48</v>
+      </c>
+      <c r="G513" s="3">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -12134,6 +12251,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12301,15 +12427,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12321,6 +12438,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12340,14 +12465,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25E5D1B-971A-414E-8466-796F2482074D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9A4DDB-F14B-4B78-A5D2-07E717BBA971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2310" yWindow="1553" windowWidth="23505" windowHeight="10350" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="66885" yWindow="1875" windowWidth="18705" windowHeight="9615" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -109,13 +109,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G513"/>
+  <dimension ref="A1:G514"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -12130,118 +12128,141 @@
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A509" s="2">
+      <c r="A509">
         <v>3051</v>
       </c>
-      <c r="B509" s="3">
+      <c r="B509">
         <v>11</v>
       </c>
-      <c r="C509" s="3">
+      <c r="C509">
         <v>15</v>
       </c>
-      <c r="D509" s="3">
+      <c r="D509">
         <v>20</v>
       </c>
-      <c r="E509" s="3">
+      <c r="E509">
         <v>21</v>
       </c>
-      <c r="F509" s="3">
+      <c r="F509">
         <v>38</v>
       </c>
-      <c r="G509" s="3">
+      <c r="G509">
         <v>48</v>
       </c>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A510" s="2">
+      <c r="A510">
         <v>3052</v>
       </c>
-      <c r="B510" s="3">
+      <c r="B510">
         <v>16</v>
       </c>
-      <c r="C510" s="3">
+      <c r="C510">
         <v>30</v>
       </c>
-      <c r="D510" s="3">
+      <c r="D510">
         <v>40</v>
       </c>
-      <c r="E510" s="3">
+      <c r="E510">
         <v>47</v>
       </c>
-      <c r="F510" s="3">
+      <c r="F510">
         <v>48</v>
       </c>
-      <c r="G510" s="3">
+      <c r="G510">
         <v>60</v>
       </c>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A511" s="2">
+      <c r="A511">
         <v>3053</v>
       </c>
-      <c r="B511" s="3">
+      <c r="B511">
         <v>1</v>
       </c>
-      <c r="C511" s="3">
+      <c r="C511">
         <v>13</v>
       </c>
-      <c r="D511" s="3">
+      <c r="D511">
         <v>25</v>
       </c>
-      <c r="E511" s="3">
+      <c r="E511">
         <v>35</v>
       </c>
-      <c r="F511" s="3">
+      <c r="F511">
         <v>39</v>
       </c>
-      <c r="G511" s="3">
+      <c r="G511">
         <v>51</v>
       </c>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A512" s="2">
+      <c r="A512">
         <v>3054</v>
       </c>
-      <c r="B512" s="3">
+      <c r="B512">
         <v>8</v>
       </c>
-      <c r="C512" s="3">
+      <c r="C512">
         <v>17</v>
       </c>
-      <c r="D512" s="3">
+      <c r="D512">
         <v>24</v>
       </c>
-      <c r="E512" s="3">
+      <c r="E512">
         <v>43</v>
       </c>
-      <c r="F512" s="3">
+      <c r="F512">
         <v>47</v>
       </c>
-      <c r="G512" s="3">
+      <c r="G512">
         <v>58</v>
       </c>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A513" s="2">
+      <c r="A513">
         <v>3055</v>
       </c>
-      <c r="B513" s="3">
+      <c r="B513">
         <v>1</v>
       </c>
-      <c r="C513" s="3">
+      <c r="C513">
         <v>11</v>
       </c>
-      <c r="D513" s="3">
+      <c r="D513">
         <v>36</v>
       </c>
-      <c r="E513" s="3">
+      <c r="E513">
         <v>43</v>
       </c>
-      <c r="F513" s="3">
+      <c r="F513">
         <v>48</v>
       </c>
-      <c r="G513" s="3">
+      <c r="G513">
         <v>49</v>
+      </c>
+    </row>
+    <row r="514" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A514">
+        <v>3056</v>
+      </c>
+      <c r="B514">
+        <v>14</v>
+      </c>
+      <c r="C514">
+        <v>21</v>
+      </c>
+      <c r="D514">
+        <v>25</v>
+      </c>
+      <c r="E514">
+        <v>40</v>
+      </c>
+      <c r="F514">
+        <v>51</v>
+      </c>
+      <c r="G514">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -12251,15 +12272,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12427,6 +12439,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12438,14 +12459,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12465,6 +12478,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9A4DDB-F14B-4B78-A5D2-07E717BBA971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45839351-5F9F-460C-818E-DCA5F0EBFD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="66885" yWindow="1875" windowWidth="18705" windowHeight="9615" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="13515" windowHeight="10372" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G514"/>
+  <dimension ref="A1:G521"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -12265,6 +12265,167 @@
         <v>56</v>
       </c>
     </row>
+    <row r="515" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A515">
+        <v>3057</v>
+      </c>
+      <c r="B515">
+        <v>2</v>
+      </c>
+      <c r="C515">
+        <v>4</v>
+      </c>
+      <c r="D515">
+        <v>16</v>
+      </c>
+      <c r="E515">
+        <v>21</v>
+      </c>
+      <c r="F515">
+        <v>48</v>
+      </c>
+      <c r="G515">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A516">
+        <v>3058</v>
+      </c>
+      <c r="B516">
+        <v>14</v>
+      </c>
+      <c r="C516">
+        <v>23</v>
+      </c>
+      <c r="D516">
+        <v>53</v>
+      </c>
+      <c r="E516">
+        <v>56</v>
+      </c>
+      <c r="F516">
+        <v>57</v>
+      </c>
+      <c r="G516">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="517" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A517">
+        <v>3059</v>
+      </c>
+      <c r="B517">
+        <v>1</v>
+      </c>
+      <c r="C517">
+        <v>2</v>
+      </c>
+      <c r="D517">
+        <v>7</v>
+      </c>
+      <c r="E517">
+        <v>18</v>
+      </c>
+      <c r="F517">
+        <v>33</v>
+      </c>
+      <c r="G517">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="518" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A518">
+        <v>3060</v>
+      </c>
+      <c r="B518">
+        <v>6</v>
+      </c>
+      <c r="C518">
+        <v>15</v>
+      </c>
+      <c r="D518">
+        <v>23</v>
+      </c>
+      <c r="E518">
+        <v>36</v>
+      </c>
+      <c r="F518">
+        <v>37</v>
+      </c>
+      <c r="G518">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="519" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A519">
+        <v>3061</v>
+      </c>
+      <c r="B519">
+        <v>24</v>
+      </c>
+      <c r="C519">
+        <v>25</v>
+      </c>
+      <c r="D519">
+        <v>28</v>
+      </c>
+      <c r="E519">
+        <v>37</v>
+      </c>
+      <c r="F519">
+        <v>47</v>
+      </c>
+      <c r="G519">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A520">
+        <v>3062</v>
+      </c>
+      <c r="B520">
+        <v>5</v>
+      </c>
+      <c r="C520">
+        <v>9</v>
+      </c>
+      <c r="D520">
+        <v>11</v>
+      </c>
+      <c r="E520">
+        <v>17</v>
+      </c>
+      <c r="F520">
+        <v>18</v>
+      </c>
+      <c r="G520">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A521">
+        <v>3063</v>
+      </c>
+      <c r="B521">
+        <v>5</v>
+      </c>
+      <c r="C521">
+        <v>35</v>
+      </c>
+      <c r="D521">
+        <v>36</v>
+      </c>
+      <c r="E521">
+        <v>41</v>
+      </c>
+      <c r="F521">
+        <v>43</v>
+      </c>
+      <c r="G521">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -12272,6 +12433,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12439,15 +12609,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12459,6 +12620,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12478,14 +12647,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>

--- a/LoteriasExcel/MegaSena_edt.xlsx
+++ b/LoteriasExcel/MegaSena_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45839351-5F9F-460C-818E-DCA5F0EBFD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDC82D8-E51F-49AF-8D90-E1C984474613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="13515" windowHeight="10372" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57675" yWindow="90" windowWidth="19845" windowHeight="11865" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="MEGA SENA" sheetId="4" r:id="rId1"/>
@@ -109,11 +109,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4E33BD-754C-4CC3-9530-49E6C4C5E994}">
-  <dimension ref="A1:G521"/>
+  <dimension ref="A1:G522"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.06640625" customWidth="1"/>
@@ -12426,6 +12428,29 @@
         <v>48</v>
       </c>
     </row>
+    <row r="522" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A522" s="2">
+        <v>3064</v>
+      </c>
+      <c r="B522" s="3">
+        <v>4</v>
+      </c>
+      <c r="C522" s="3">
+        <v>10</v>
+      </c>
+      <c r="D522" s="3">
+        <v>20</v>
+      </c>
+      <c r="E522" s="3">
+        <v>25</v>
+      </c>
+      <c r="F522" s="3">
+        <v>27</v>
+      </c>
+      <c r="G522" s="3">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -12433,15 +12458,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12609,6 +12625,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12620,14 +12645,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9445F805-6E3A-4841-AEBD-CF7F6CDA924D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12647,6 +12664,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{834FBCC7-87B2-49AB-8978-479962E2FF95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64615F65-CF13-4100-B135-FA0CB5E1C951}">
   <ds:schemaRefs>
